--- a/Result/profitability/6417.xlsx
+++ b/Result/profitability/6417.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7542,6 +7542,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6417</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>506</v>
+      </c>
+      <c r="D57" t="n">
+        <v>331</v>
+      </c>
+      <c r="E57" t="n">
+        <v>176</v>
+      </c>
+      <c r="F57" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="G57" t="n">
+        <v>106</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>20.95%</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>106</v>
+      </c>
+      <c r="K57" t="n">
+        <v>82</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.35875</v>
+      </c>
+      <c r="N57" t="n">
+        <v>31.90875</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.1616766467065869</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.004049754122071203</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>2.03125</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.1096547314578005</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK57" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
